--- a/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2023_aysen_sexo.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2023_aysen_sexo.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 15:09</t>
+    <t xml:space="preserve">2026-10-05 06:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -537,7 +537,7 @@
         <v>4.1</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
